--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:50:25+00:00</t>
+    <t>2026-06-24T08:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
